--- a/DEVELOPMENT_ALL_OLD_NEW/HOLLISTER/HR.0291 HGUYS6006.xlsx
+++ b/DEVELOPMENT_ALL_OLD_NEW/HOLLISTER/HR.0291 HGUYS6006.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_580400FA6265EC019C1427B22A0F1055643F244A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -267,7 +268,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General_)"/>
   </numFmts>
@@ -1414,12 +1415,271 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="5" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="44" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="5" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="44" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="2" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="2" borderId="43" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="2" borderId="44" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="2" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="2" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="2" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="2" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="2" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="2" borderId="30" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="2" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="31" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="32" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="33" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="35" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="27" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="4" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="4" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="4" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="39" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="24" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="2" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="2" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="2" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="17" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="36" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="37" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="39" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="2" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="2" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="2" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="16" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="5" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="5" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1429,9 +1689,6 @@
     <xf numFmtId="164" fontId="15" fillId="2" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="2" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="15" fillId="2" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1463,270 +1720,14 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="20" fillId="5" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="16" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="2" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="2" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="17" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="36" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="37" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="39" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="2" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="2" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="2" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="39" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="24" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="27" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="2" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="2" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="2" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="2" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="2" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="2" borderId="30" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="2" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="31" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="32" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="33" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="35" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="4" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="4" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="4" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="44" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="5" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="44" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="2" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="2" borderId="43" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="2" borderId="44" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2 3" xfId="1"/>
-    <cellStyle name="Normal 3 2" xfId="3"/>
-    <cellStyle name="Normal_0136" xfId="2"/>
+    <cellStyle name="Normal 2 3" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Normal 3 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Normal_0136" xfId="2" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2003,26 +2004,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K72"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="62.7109375" customWidth="1"/>
-    <col min="3" max="3" width="25.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.28515625" customWidth="1"/>
-    <col min="5" max="5" width="25.28515625" customWidth="1"/>
+    <col min="2" max="2" width="62.6640625" customWidth="1"/>
+    <col min="3" max="3" width="25.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.33203125" customWidth="1"/>
+    <col min="5" max="5" width="25.33203125" customWidth="1"/>
     <col min="6" max="6" width="23" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="59.7109375" customWidth="1"/>
-    <col min="8" max="8" width="19.5703125" customWidth="1"/>
-    <col min="9" max="9" width="46.85546875" customWidth="1"/>
-    <col min="10" max="10" width="30.85546875" customWidth="1"/>
-    <col min="11" max="11" width="27.140625" customWidth="1"/>
+    <col min="7" max="7" width="59.6640625" customWidth="1"/>
+    <col min="8" max="8" width="19.5546875" customWidth="1"/>
+    <col min="9" max="9" width="46.88671875" customWidth="1"/>
+    <col min="10" max="10" width="30.88671875" customWidth="1"/>
+    <col min="11" max="11" width="27.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="44.25">
+    <row r="1" spans="1:11" ht="44.4">
       <c r="A1" s="1"/>
       <c r="B1" s="9" t="s">
         <v>1</v>
@@ -2042,38 +2043,38 @@
       <c r="B2" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="164">
+      <c r="C2" s="114">
         <v>46219</v>
       </c>
-      <c r="D2" s="165"/>
-      <c r="E2" s="166"/>
-      <c r="F2" s="164" t="s">
+      <c r="D2" s="115"/>
+      <c r="E2" s="116"/>
+      <c r="F2" s="114" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="165"/>
-      <c r="H2" s="167" t="s">
+      <c r="G2" s="115"/>
+      <c r="H2" s="117" t="s">
         <v>69</v>
       </c>
-      <c r="I2" s="168"/>
-      <c r="J2" s="168"/>
-      <c r="K2" s="169"/>
+      <c r="I2" s="118"/>
+      <c r="J2" s="118"/>
+      <c r="K2" s="119"/>
     </row>
     <row r="3" spans="1:11" ht="60" customHeight="1">
       <c r="A3" s="2"/>
       <c r="B3" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="170" t="s">
+      <c r="C3" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="D3" s="165"/>
-      <c r="E3" s="166"/>
-      <c r="F3" s="171"/>
-      <c r="G3" s="172"/>
-      <c r="H3" s="177" t="s">
+      <c r="D3" s="115"/>
+      <c r="E3" s="116"/>
+      <c r="F3" s="121"/>
+      <c r="G3" s="122"/>
+      <c r="H3" s="127" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="178"/>
+      <c r="I3" s="128"/>
       <c r="J3" s="11"/>
       <c r="K3" s="12"/>
     </row>
@@ -2082,179 +2083,179 @@
       <c r="B4" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="179" t="s">
+      <c r="C4" s="129" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="180"/>
-      <c r="E4" s="181"/>
-      <c r="F4" s="173"/>
-      <c r="G4" s="174"/>
-      <c r="H4" s="153"/>
-      <c r="I4" s="154"/>
-      <c r="J4" s="153"/>
-      <c r="K4" s="154"/>
+      <c r="D4" s="130"/>
+      <c r="E4" s="131"/>
+      <c r="F4" s="123"/>
+      <c r="G4" s="124"/>
+      <c r="H4" s="132"/>
+      <c r="I4" s="133"/>
+      <c r="J4" s="132"/>
+      <c r="K4" s="133"/>
     </row>
     <row r="5" spans="1:11" ht="45">
       <c r="A5" s="2"/>
       <c r="B5" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="179">
+      <c r="C5" s="129">
         <v>51311586</v>
       </c>
-      <c r="D5" s="180"/>
-      <c r="E5" s="181"/>
-      <c r="F5" s="173"/>
-      <c r="G5" s="174"/>
-      <c r="H5" s="153"/>
-      <c r="I5" s="154"/>
-      <c r="J5" s="153"/>
-      <c r="K5" s="154"/>
+      <c r="D5" s="130"/>
+      <c r="E5" s="131"/>
+      <c r="F5" s="123"/>
+      <c r="G5" s="124"/>
+      <c r="H5" s="132"/>
+      <c r="I5" s="133"/>
+      <c r="J5" s="132"/>
+      <c r="K5" s="133"/>
     </row>
     <row r="6" spans="1:11" ht="45">
       <c r="A6" s="2"/>
       <c r="B6" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="182" t="s">
+      <c r="C6" s="134" t="s">
         <v>0</v>
       </c>
-      <c r="D6" s="183"/>
-      <c r="E6" s="184"/>
-      <c r="F6" s="173"/>
-      <c r="G6" s="174"/>
-      <c r="H6" s="153"/>
-      <c r="I6" s="154"/>
-      <c r="J6" s="153"/>
-      <c r="K6" s="154"/>
+      <c r="D6" s="135"/>
+      <c r="E6" s="136"/>
+      <c r="F6" s="123"/>
+      <c r="G6" s="124"/>
+      <c r="H6" s="132"/>
+      <c r="I6" s="133"/>
+      <c r="J6" s="132"/>
+      <c r="K6" s="133"/>
     </row>
     <row r="7" spans="1:11" ht="60" customHeight="1">
       <c r="A7" s="2"/>
       <c r="B7" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="161" t="s">
+      <c r="C7" s="143" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="162"/>
-      <c r="E7" s="163"/>
-      <c r="F7" s="173"/>
-      <c r="G7" s="174"/>
-      <c r="H7" s="153"/>
-      <c r="I7" s="154"/>
-      <c r="J7" s="153"/>
-      <c r="K7" s="154"/>
+      <c r="D7" s="144"/>
+      <c r="E7" s="145"/>
+      <c r="F7" s="123"/>
+      <c r="G7" s="124"/>
+      <c r="H7" s="132"/>
+      <c r="I7" s="133"/>
+      <c r="J7" s="132"/>
+      <c r="K7" s="133"/>
     </row>
     <row r="8" spans="1:11" ht="45">
       <c r="A8" s="2"/>
       <c r="B8" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="185"/>
-      <c r="D8" s="186"/>
-      <c r="E8" s="187"/>
-      <c r="F8" s="173"/>
-      <c r="G8" s="174"/>
+      <c r="C8" s="137"/>
+      <c r="D8" s="138"/>
+      <c r="E8" s="139"/>
+      <c r="F8" s="123"/>
+      <c r="G8" s="124"/>
       <c r="H8" s="11"/>
       <c r="I8" s="12"/>
-      <c r="J8" s="153"/>
-      <c r="K8" s="154"/>
+      <c r="J8" s="132"/>
+      <c r="K8" s="133"/>
     </row>
     <row r="9" spans="1:11" ht="45">
       <c r="A9" s="2"/>
       <c r="B9" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="158">
+      <c r="C9" s="140">
         <v>11</v>
       </c>
-      <c r="D9" s="159"/>
-      <c r="E9" s="160"/>
-      <c r="F9" s="173"/>
-      <c r="G9" s="174"/>
+      <c r="D9" s="141"/>
+      <c r="E9" s="142"/>
+      <c r="F9" s="123"/>
+      <c r="G9" s="124"/>
       <c r="H9" s="11"/>
       <c r="I9" s="12"/>
-      <c r="J9" s="153"/>
-      <c r="K9" s="154"/>
+      <c r="J9" s="132"/>
+      <c r="K9" s="133"/>
     </row>
     <row r="10" spans="1:11" ht="45">
       <c r="A10" s="2"/>
       <c r="B10" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="158"/>
-      <c r="D10" s="159"/>
-      <c r="E10" s="160"/>
-      <c r="F10" s="173"/>
-      <c r="G10" s="174"/>
+      <c r="C10" s="140"/>
+      <c r="D10" s="141"/>
+      <c r="E10" s="142"/>
+      <c r="F10" s="123"/>
+      <c r="G10" s="124"/>
       <c r="H10" s="11"/>
       <c r="I10" s="12"/>
-      <c r="J10" s="153"/>
-      <c r="K10" s="154"/>
+      <c r="J10" s="132"/>
+      <c r="K10" s="133"/>
     </row>
     <row r="11" spans="1:11" ht="45">
       <c r="A11" s="2"/>
       <c r="B11" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="155"/>
-      <c r="D11" s="156"/>
-      <c r="E11" s="157"/>
-      <c r="F11" s="173"/>
-      <c r="G11" s="174"/>
-      <c r="H11" s="153"/>
-      <c r="I11" s="154"/>
-      <c r="J11" s="153"/>
-      <c r="K11" s="154"/>
+      <c r="C11" s="146"/>
+      <c r="D11" s="147"/>
+      <c r="E11" s="148"/>
+      <c r="F11" s="123"/>
+      <c r="G11" s="124"/>
+      <c r="H11" s="132"/>
+      <c r="I11" s="133"/>
+      <c r="J11" s="132"/>
+      <c r="K11" s="133"/>
     </row>
     <row r="12" spans="1:11" ht="45">
       <c r="A12" s="2"/>
       <c r="B12" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="150" t="s">
+      <c r="C12" s="152" t="s">
         <v>17</v>
       </c>
-      <c r="D12" s="151"/>
-      <c r="E12" s="152"/>
-      <c r="F12" s="173"/>
-      <c r="G12" s="174"/>
-      <c r="H12" s="153"/>
-      <c r="I12" s="154"/>
-      <c r="J12" s="153"/>
-      <c r="K12" s="154"/>
+      <c r="D12" s="153"/>
+      <c r="E12" s="154"/>
+      <c r="F12" s="123"/>
+      <c r="G12" s="124"/>
+      <c r="H12" s="132"/>
+      <c r="I12" s="133"/>
+      <c r="J12" s="132"/>
+      <c r="K12" s="133"/>
     </row>
     <row r="13" spans="1:11" ht="45">
       <c r="A13" s="2"/>
       <c r="B13" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="155"/>
-      <c r="D13" s="156"/>
-      <c r="E13" s="157"/>
-      <c r="F13" s="175"/>
-      <c r="G13" s="176"/>
-      <c r="H13" s="153"/>
-      <c r="I13" s="154"/>
-      <c r="J13" s="153"/>
-      <c r="K13" s="154"/>
-    </row>
-    <row r="14" spans="1:11" ht="46.5">
+      <c r="C13" s="146"/>
+      <c r="D13" s="147"/>
+      <c r="E13" s="148"/>
+      <c r="F13" s="125"/>
+      <c r="G13" s="126"/>
+      <c r="H13" s="132"/>
+      <c r="I13" s="133"/>
+      <c r="J13" s="132"/>
+      <c r="K13" s="133"/>
+    </row>
+    <row r="14" spans="1:11" ht="46.2">
       <c r="A14" s="2"/>
       <c r="B14" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="129"/>
-      <c r="D14" s="129"/>
-      <c r="E14" s="130"/>
-      <c r="F14" s="131" t="s">
+      <c r="C14" s="156"/>
+      <c r="D14" s="156"/>
+      <c r="E14" s="157"/>
+      <c r="F14" s="158" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="132"/>
-      <c r="H14" s="135" t="s">
+      <c r="G14" s="159"/>
+      <c r="H14" s="162" t="s">
         <v>21</v>
       </c>
-      <c r="I14" s="136"/>
+      <c r="I14" s="163"/>
       <c r="J14" s="17"/>
       <c r="K14" s="18"/>
     </row>
@@ -2270,14 +2271,14 @@
       <c r="E15" s="16">
         <v>1</v>
       </c>
-      <c r="F15" s="133"/>
-      <c r="G15" s="134"/>
-      <c r="H15" s="133"/>
-      <c r="I15" s="137"/>
-      <c r="J15" s="138" t="s">
+      <c r="F15" s="160"/>
+      <c r="G15" s="161"/>
+      <c r="H15" s="160"/>
+      <c r="I15" s="164"/>
+      <c r="J15" s="165" t="s">
         <v>23</v>
       </c>
-      <c r="K15" s="147" t="s">
+      <c r="K15" s="149" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2301,29 +2302,29 @@
       <c r="G16" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H16" s="149" t="s">
+      <c r="H16" s="151" t="s">
         <v>30</v>
       </c>
-      <c r="I16" s="149"/>
-      <c r="J16" s="139"/>
-      <c r="K16" s="148"/>
-    </row>
-    <row r="17" spans="1:11" ht="36">
+      <c r="I16" s="151"/>
+      <c r="J16" s="166"/>
+      <c r="K16" s="150"/>
+    </row>
+    <row r="17" spans="1:11" ht="36.6">
       <c r="A17" s="4"/>
       <c r="B17" s="28"/>
-      <c r="C17" s="140" t="s">
+      <c r="C17" s="167" t="s">
         <v>31</v>
       </c>
-      <c r="D17" s="141"/>
-      <c r="E17" s="141"/>
-      <c r="F17" s="141"/>
-      <c r="G17" s="141"/>
-      <c r="H17" s="141"/>
-      <c r="I17" s="142"/>
+      <c r="D17" s="168"/>
+      <c r="E17" s="168"/>
+      <c r="F17" s="168"/>
+      <c r="G17" s="168"/>
+      <c r="H17" s="168"/>
+      <c r="I17" s="169"/>
       <c r="J17" s="29"/>
       <c r="K17" s="30"/>
     </row>
-    <row r="18" spans="1:11" ht="36">
+    <row r="18" spans="1:11" ht="36.6">
       <c r="A18" s="4"/>
       <c r="B18" s="28" t="s">
         <v>70</v>
@@ -2338,7 +2339,7 @@
       <c r="J18" s="29"/>
       <c r="K18" s="30"/>
     </row>
-    <row r="19" spans="1:11" ht="36">
+    <row r="19" spans="1:11" ht="36.6">
       <c r="A19" s="4"/>
       <c r="B19" s="34" t="s">
         <v>32</v>
@@ -2353,7 +2354,7 @@
       <c r="J19" s="36"/>
       <c r="K19" s="37"/>
     </row>
-    <row r="20" spans="1:11" ht="36">
+    <row r="20" spans="1:11" ht="36.6">
       <c r="A20" s="4"/>
       <c r="B20" s="22"/>
       <c r="C20" s="23"/>
@@ -2366,7 +2367,7 @@
       <c r="J20" s="27"/>
       <c r="K20" s="27"/>
     </row>
-    <row r="21" spans="1:11" ht="36">
+    <row r="21" spans="1:11" ht="36.6">
       <c r="A21" s="4"/>
       <c r="B21" s="38" t="s">
         <v>33</v>
@@ -2384,14 +2385,14 @@
       <c r="G21" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="H21" s="143" t="s">
+      <c r="H21" s="170" t="s">
         <v>35</v>
       </c>
-      <c r="I21" s="144"/>
+      <c r="I21" s="171"/>
       <c r="J21" s="29"/>
       <c r="K21" s="30"/>
     </row>
-    <row r="22" spans="1:11" ht="36">
+    <row r="22" spans="1:11" ht="36.6">
       <c r="A22" s="4"/>
       <c r="B22" s="41" t="s">
         <v>36</v>
@@ -2411,14 +2412,14 @@
       <c r="G22" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="H22" s="143" t="s">
+      <c r="H22" s="170" t="s">
         <v>57</v>
       </c>
-      <c r="I22" s="144"/>
+      <c r="I22" s="171"/>
       <c r="J22" s="29"/>
       <c r="K22" s="30"/>
     </row>
-    <row r="23" spans="1:11" ht="36">
+    <row r="23" spans="1:11" ht="36.6">
       <c r="A23" s="4"/>
       <c r="B23" s="41"/>
       <c r="C23" s="43"/>
@@ -2432,14 +2433,14 @@
       <c r="G23" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="H23" s="143" t="s">
+      <c r="H23" s="170" t="s">
         <v>58</v>
       </c>
-      <c r="I23" s="144"/>
+      <c r="I23" s="171"/>
       <c r="J23" s="29"/>
       <c r="K23" s="30"/>
     </row>
-    <row r="24" spans="1:11" ht="36">
+    <row r="24" spans="1:11" ht="36.6">
       <c r="A24" s="4"/>
       <c r="B24" s="41"/>
       <c r="C24" s="43"/>
@@ -2471,7 +2472,7 @@
       <c r="J25" s="50"/>
       <c r="K25" s="51"/>
     </row>
-    <row r="26" spans="1:11" ht="36">
+    <row r="26" spans="1:11" ht="36.6">
       <c r="A26" s="4"/>
       <c r="B26" s="38" t="s">
         <v>59</v>
@@ -2491,14 +2492,14 @@
       <c r="G26" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="H26" s="146" t="s">
+      <c r="H26" s="173" t="s">
         <v>60</v>
       </c>
-      <c r="I26" s="146"/>
+      <c r="I26" s="173"/>
       <c r="J26" s="29"/>
       <c r="K26" s="30"/>
     </row>
-    <row r="27" spans="1:11" ht="36">
+    <row r="27" spans="1:11" ht="36.6">
       <c r="A27" s="4"/>
       <c r="B27" s="53"/>
       <c r="C27" s="54"/>
@@ -2524,7 +2525,7 @@
       <c r="J28" s="57"/>
       <c r="K28" s="58"/>
     </row>
-    <row r="29" spans="1:11" ht="36">
+    <row r="29" spans="1:11" ht="36.6">
       <c r="A29" s="4"/>
       <c r="B29" s="93" t="s">
         <v>73</v>
@@ -2544,10 +2545,10 @@
       <c r="G29" s="59" t="s">
         <v>61</v>
       </c>
-      <c r="H29" s="146" t="s">
+      <c r="H29" s="173" t="s">
         <v>74</v>
       </c>
-      <c r="I29" s="146"/>
+      <c r="I29" s="173"/>
       <c r="J29" s="29"/>
       <c r="K29" s="94"/>
     </row>
@@ -2571,10 +2572,10 @@
       <c r="G30" s="59" t="s">
         <v>62</v>
       </c>
-      <c r="H30" s="145" t="s">
+      <c r="H30" s="172" t="s">
         <v>63</v>
       </c>
-      <c r="I30" s="145"/>
+      <c r="I30" s="172"/>
       <c r="J30" s="60"/>
       <c r="K30" s="95"/>
     </row>
@@ -2592,12 +2593,12 @@
       <c r="E31" s="39"/>
       <c r="F31" s="30"/>
       <c r="G31" s="59"/>
-      <c r="H31" s="145"/>
-      <c r="I31" s="145"/>
+      <c r="H31" s="172"/>
+      <c r="I31" s="172"/>
       <c r="J31" s="60"/>
       <c r="K31" s="95"/>
     </row>
-    <row r="32" spans="1:11" ht="36">
+    <row r="32" spans="1:11" ht="36.6">
       <c r="A32" s="4"/>
       <c r="B32" s="53"/>
       <c r="C32" s="54"/>
@@ -2618,12 +2619,12 @@
       <c r="E33" s="30"/>
       <c r="F33" s="30"/>
       <c r="G33" s="59"/>
-      <c r="H33" s="146"/>
-      <c r="I33" s="146"/>
+      <c r="H33" s="173"/>
+      <c r="I33" s="173"/>
       <c r="J33" s="29"/>
       <c r="K33" s="94"/>
     </row>
-    <row r="34" spans="1:11" ht="36">
+    <row r="34" spans="1:11" ht="36.6">
       <c r="A34" s="4"/>
       <c r="B34" s="52"/>
       <c r="C34" s="39"/>
@@ -2631,8 +2632,8 @@
       <c r="E34" s="39"/>
       <c r="F34" s="30"/>
       <c r="G34" s="59"/>
-      <c r="H34" s="145"/>
-      <c r="I34" s="145"/>
+      <c r="H34" s="172"/>
+      <c r="I34" s="172"/>
       <c r="J34" s="60"/>
       <c r="K34" s="95"/>
     </row>
@@ -2649,7 +2650,7 @@
       <c r="J35" s="63"/>
       <c r="K35" s="63"/>
     </row>
-    <row r="36" spans="1:11" ht="36">
+    <row r="36" spans="1:11" ht="36.6">
       <c r="A36" s="4"/>
       <c r="B36" s="41" t="s">
         <v>40</v>
@@ -2665,10 +2666,10 @@
       <c r="G36" s="60" t="s">
         <v>34</v>
       </c>
-      <c r="H36" s="107" t="s">
+      <c r="H36" s="174" t="s">
         <v>41</v>
       </c>
-      <c r="I36" s="107"/>
+      <c r="I36" s="174"/>
       <c r="J36" s="60"/>
       <c r="K36" s="60"/>
     </row>
@@ -2686,21 +2687,21 @@
       <c r="E37" s="39"/>
       <c r="F37" s="60"/>
       <c r="G37" s="59"/>
-      <c r="H37" s="107"/>
-      <c r="I37" s="107"/>
+      <c r="H37" s="174"/>
+      <c r="I37" s="174"/>
       <c r="J37" s="60"/>
       <c r="K37" s="60"/>
     </row>
     <row r="38" spans="1:11" ht="36.6" customHeight="1">
       <c r="A38" s="4"/>
       <c r="B38" s="22"/>
-      <c r="C38" s="111" t="s">
+      <c r="C38" s="155" t="s">
         <v>64</v>
       </c>
-      <c r="D38" s="111"/>
-      <c r="E38" s="111"/>
-      <c r="F38" s="111"/>
-      <c r="G38" s="111"/>
+      <c r="D38" s="155"/>
+      <c r="E38" s="155"/>
+      <c r="F38" s="155"/>
+      <c r="G38" s="155"/>
       <c r="H38" s="22"/>
       <c r="I38" s="22"/>
       <c r="J38" s="24"/>
@@ -2726,14 +2727,14 @@
       <c r="G39" s="67" t="s">
         <v>34</v>
       </c>
-      <c r="H39" s="123" t="s">
+      <c r="H39" s="175" t="s">
         <v>45</v>
       </c>
-      <c r="I39" s="124"/>
+      <c r="I39" s="176"/>
       <c r="J39" s="66"/>
       <c r="K39" s="66"/>
     </row>
-    <row r="40" spans="1:11" ht="36">
+    <row r="40" spans="1:11" ht="36.6">
       <c r="A40" s="4"/>
       <c r="B40" s="70" t="s">
         <v>49</v>
@@ -2751,14 +2752,14 @@
       <c r="G40" s="67" t="s">
         <v>34</v>
       </c>
-      <c r="H40" s="123" t="s">
+      <c r="H40" s="175" t="s">
         <v>66</v>
       </c>
-      <c r="I40" s="124"/>
+      <c r="I40" s="176"/>
       <c r="J40" s="66"/>
       <c r="K40" s="66"/>
     </row>
-    <row r="41" spans="1:11" ht="36">
+    <row r="41" spans="1:11" ht="36.6">
       <c r="A41" s="4"/>
       <c r="B41" s="22"/>
       <c r="C41" s="23"/>
@@ -2791,14 +2792,14 @@
       <c r="G42" s="73" t="s">
         <v>34</v>
       </c>
-      <c r="H42" s="114" t="s">
+      <c r="H42" s="187" t="s">
         <v>48</v>
       </c>
-      <c r="I42" s="115"/>
+      <c r="I42" s="188"/>
       <c r="J42" s="30"/>
       <c r="K42" s="30"/>
     </row>
-    <row r="43" spans="1:11" ht="36">
+    <row r="43" spans="1:11" ht="36.6">
       <c r="A43" s="4"/>
       <c r="B43" s="52" t="s">
         <v>49</v>
@@ -2818,14 +2819,14 @@
       <c r="G43" s="73" t="s">
         <v>34</v>
       </c>
-      <c r="H43" s="118" t="s">
+      <c r="H43" s="191" t="s">
         <v>77</v>
       </c>
-      <c r="I43" s="119"/>
+      <c r="I43" s="192"/>
       <c r="J43" s="30"/>
       <c r="K43" s="30"/>
     </row>
-    <row r="44" spans="1:11" ht="36">
+    <row r="44" spans="1:11" ht="36.6">
       <c r="A44" s="4"/>
       <c r="B44" s="52" t="s">
         <v>56</v>
@@ -2840,22 +2841,22 @@
       <c r="J44" s="30"/>
       <c r="K44" s="105"/>
     </row>
-    <row r="45" spans="1:11" ht="36">
+    <row r="45" spans="1:11" ht="36.6">
       <c r="A45" s="4"/>
       <c r="B45" s="74"/>
-      <c r="C45" s="110" t="s">
+      <c r="C45" s="184" t="s">
         <v>75</v>
       </c>
-      <c r="D45" s="111"/>
-      <c r="E45" s="111"/>
-      <c r="F45" s="111"/>
-      <c r="G45" s="112"/>
+      <c r="D45" s="155"/>
+      <c r="E45" s="155"/>
+      <c r="F45" s="155"/>
+      <c r="G45" s="185"/>
       <c r="H45" s="75"/>
       <c r="I45" s="76"/>
       <c r="J45" s="63"/>
       <c r="K45" s="77"/>
     </row>
-    <row r="46" spans="1:11" ht="36">
+    <row r="46" spans="1:11" ht="36.6">
       <c r="A46" s="4"/>
       <c r="B46" s="52" t="s">
         <v>43</v>
@@ -2867,10 +2868,10 @@
       <c r="G46" s="73" t="s">
         <v>34</v>
       </c>
-      <c r="H46" s="107" t="s">
+      <c r="H46" s="174" t="s">
         <v>44</v>
       </c>
-      <c r="I46" s="107"/>
+      <c r="I46" s="174"/>
       <c r="J46" s="60"/>
       <c r="K46" s="60"/>
     </row>
@@ -2884,14 +2885,14 @@
       <c r="G47" s="73" t="s">
         <v>34</v>
       </c>
-      <c r="H47" s="107" t="s">
+      <c r="H47" s="174" t="s">
         <v>45</v>
       </c>
-      <c r="I47" s="107"/>
+      <c r="I47" s="174"/>
       <c r="J47" s="60"/>
       <c r="K47" s="60"/>
     </row>
-    <row r="48" spans="1:11" ht="36">
+    <row r="48" spans="1:11" ht="36.6">
       <c r="A48" s="4"/>
       <c r="B48" s="78"/>
       <c r="C48" s="39"/>
@@ -2901,29 +2902,29 @@
       <c r="G48" s="73" t="s">
         <v>34</v>
       </c>
-      <c r="H48" s="107" t="s">
+      <c r="H48" s="174" t="s">
         <v>46</v>
       </c>
-      <c r="I48" s="107"/>
+      <c r="I48" s="174"/>
       <c r="J48" s="60"/>
       <c r="K48" s="60"/>
     </row>
-    <row r="49" spans="1:11" ht="36">
+    <row r="49" spans="1:11" ht="36.6">
       <c r="A49" s="4"/>
-      <c r="B49" s="190"/>
-      <c r="C49" s="193" t="s">
+      <c r="B49" s="108"/>
+      <c r="C49" s="111" t="s">
         <v>78</v>
       </c>
-      <c r="D49" s="194"/>
-      <c r="E49" s="194"/>
-      <c r="F49" s="194"/>
-      <c r="G49" s="195"/>
-      <c r="H49" s="191"/>
-      <c r="I49" s="192"/>
+      <c r="D49" s="112"/>
+      <c r="E49" s="112"/>
+      <c r="F49" s="112"/>
+      <c r="G49" s="113"/>
+      <c r="H49" s="109"/>
+      <c r="I49" s="110"/>
       <c r="J49" s="51"/>
       <c r="K49" s="51"/>
     </row>
-    <row r="50" spans="1:11" ht="36">
+    <row r="50" spans="1:11" ht="36.6">
       <c r="A50" s="4"/>
       <c r="B50" s="78"/>
       <c r="C50" s="39">
@@ -2935,14 +2936,14 @@
       <c r="G50" s="102">
         <v>1</v>
       </c>
-      <c r="H50" s="188" t="s">
+      <c r="H50" s="106" t="s">
         <v>79</v>
       </c>
-      <c r="I50" s="189"/>
+      <c r="I50" s="107"/>
       <c r="J50" s="60"/>
       <c r="K50" s="60"/>
     </row>
-    <row r="51" spans="1:11" ht="36">
+    <row r="51" spans="1:11" ht="36.6">
       <c r="A51" s="4"/>
       <c r="B51" s="78"/>
       <c r="C51" s="39"/>
@@ -2952,14 +2953,14 @@
       <c r="G51" s="102">
         <v>5</v>
       </c>
-      <c r="H51" s="188" t="s">
+      <c r="H51" s="106" t="s">
         <v>80</v>
       </c>
-      <c r="I51" s="189"/>
+      <c r="I51" s="107"/>
       <c r="J51" s="60"/>
       <c r="K51" s="60"/>
     </row>
-    <row r="52" spans="1:11" ht="36">
+    <row r="52" spans="1:11" ht="36.6">
       <c r="A52" s="4"/>
       <c r="B52" s="78"/>
       <c r="C52" s="39"/>
@@ -2969,14 +2970,14 @@
       <c r="G52" s="102">
         <v>1</v>
       </c>
-      <c r="H52" s="188" t="s">
+      <c r="H52" s="106" t="s">
         <v>46</v>
       </c>
-      <c r="I52" s="189"/>
+      <c r="I52" s="107"/>
       <c r="J52" s="60"/>
       <c r="K52" s="60"/>
     </row>
-    <row r="53" spans="1:11" ht="36">
+    <row r="53" spans="1:11" ht="36.6">
       <c r="A53" s="4"/>
       <c r="B53" s="61"/>
       <c r="C53" s="62"/>
@@ -3009,14 +3010,14 @@
       <c r="G54" s="80" t="s">
         <v>34</v>
       </c>
-      <c r="H54" s="116" t="s">
+      <c r="H54" s="189" t="s">
         <v>48</v>
       </c>
-      <c r="I54" s="117"/>
+      <c r="I54" s="190"/>
       <c r="J54" s="30"/>
       <c r="K54" s="30"/>
     </row>
-    <row r="55" spans="1:11" ht="36">
+    <row r="55" spans="1:11" ht="36.6">
       <c r="A55" s="4"/>
       <c r="B55" s="81" t="s">
         <v>42</v>
@@ -3036,14 +3037,14 @@
       <c r="G55" s="80" t="s">
         <v>34</v>
       </c>
-      <c r="H55" s="107" t="s">
+      <c r="H55" s="174" t="s">
         <v>77</v>
       </c>
-      <c r="I55" s="107"/>
+      <c r="I55" s="174"/>
       <c r="J55" s="59"/>
       <c r="K55" s="59"/>
     </row>
-    <row r="56" spans="1:11" ht="36">
+    <row r="56" spans="1:11" ht="36.6">
       <c r="A56" s="4"/>
       <c r="B56" s="84"/>
       <c r="C56" s="83"/>
@@ -3051,25 +3052,25 @@
       <c r="E56" s="83"/>
       <c r="F56" s="59"/>
       <c r="G56" s="59"/>
-      <c r="H56" s="113"/>
-      <c r="I56" s="113"/>
+      <c r="H56" s="186"/>
+      <c r="I56" s="186"/>
       <c r="J56" s="59"/>
       <c r="K56" s="59"/>
     </row>
     <row r="57" spans="1:11" ht="36.6" customHeight="1">
       <c r="A57" s="4"/>
       <c r="B57" s="74"/>
-      <c r="C57" s="120"/>
-      <c r="D57" s="121"/>
-      <c r="E57" s="121"/>
-      <c r="F57" s="121"/>
-      <c r="G57" s="122"/>
-      <c r="H57" s="108"/>
-      <c r="I57" s="109"/>
+      <c r="C57" s="193"/>
+      <c r="D57" s="194"/>
+      <c r="E57" s="194"/>
+      <c r="F57" s="194"/>
+      <c r="G57" s="195"/>
+      <c r="H57" s="182"/>
+      <c r="I57" s="183"/>
       <c r="J57" s="51"/>
       <c r="K57" s="51"/>
     </row>
-    <row r="58" spans="1:11" ht="36">
+    <row r="58" spans="1:11" ht="36.6">
       <c r="A58" s="6"/>
       <c r="B58" s="96" t="s">
         <v>50</v>
@@ -3087,14 +3088,14 @@
       <c r="G58" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="H58" s="123" t="s">
+      <c r="H58" s="175" t="s">
         <v>52</v>
       </c>
-      <c r="I58" s="124"/>
+      <c r="I58" s="176"/>
       <c r="J58" s="66"/>
       <c r="K58" s="97"/>
     </row>
-    <row r="59" spans="1:11" ht="72">
+    <row r="59" spans="1:11" ht="73.2">
       <c r="A59" s="6"/>
       <c r="B59" s="96"/>
       <c r="C59" s="65"/>
@@ -3113,7 +3114,7 @@
       <c r="J59" s="66"/>
       <c r="K59" s="97"/>
     </row>
-    <row r="60" spans="1:11" ht="72">
+    <row r="60" spans="1:11" ht="73.2">
       <c r="A60" s="6"/>
       <c r="B60" s="96" t="s">
         <v>36</v>
@@ -3134,16 +3135,16 @@
       <c r="J60" s="66"/>
       <c r="K60" s="97"/>
     </row>
-    <row r="61" spans="1:11" ht="36">
+    <row r="61" spans="1:11" ht="36.6">
       <c r="A61" s="6"/>
       <c r="B61" s="74"/>
-      <c r="C61" s="120"/>
-      <c r="D61" s="121"/>
-      <c r="E61" s="121"/>
-      <c r="F61" s="121"/>
-      <c r="G61" s="122"/>
-      <c r="H61" s="108"/>
-      <c r="I61" s="109"/>
+      <c r="C61" s="193"/>
+      <c r="D61" s="194"/>
+      <c r="E61" s="194"/>
+      <c r="F61" s="194"/>
+      <c r="G61" s="195"/>
+      <c r="H61" s="182"/>
+      <c r="I61" s="183"/>
       <c r="J61" s="51"/>
       <c r="K61" s="51"/>
     </row>
@@ -3151,16 +3152,16 @@
       <c r="A62" s="6"/>
       <c r="B62" s="74"/>
       <c r="C62" s="85"/>
-      <c r="D62" s="106"/>
-      <c r="E62" s="106"/>
+      <c r="D62" s="181"/>
+      <c r="E62" s="181"/>
       <c r="F62" s="51"/>
       <c r="G62" s="51"/>
-      <c r="H62" s="128"/>
-      <c r="I62" s="128"/>
+      <c r="H62" s="180"/>
+      <c r="I62" s="180"/>
       <c r="J62" s="51"/>
       <c r="K62" s="51"/>
     </row>
-    <row r="63" spans="1:11" ht="36">
+    <row r="63" spans="1:11" ht="36.6">
       <c r="A63" s="6"/>
       <c r="B63" s="86" t="s">
         <v>54</v>
@@ -3180,14 +3181,14 @@
       <c r="G63" s="90" t="s">
         <v>67</v>
       </c>
-      <c r="H63" s="125" t="s">
+      <c r="H63" s="177" t="s">
         <v>55</v>
       </c>
-      <c r="I63" s="125"/>
+      <c r="I63" s="177"/>
       <c r="J63" s="60"/>
       <c r="K63" s="59"/>
     </row>
-    <row r="64" spans="1:11" ht="36">
+    <row r="64" spans="1:11" ht="36.6">
       <c r="A64" s="6"/>
       <c r="B64" s="52" t="s">
         <v>56</v>
@@ -3197,12 +3198,12 @@
       <c r="E64" s="60"/>
       <c r="F64" s="91"/>
       <c r="G64" s="59"/>
-      <c r="H64" s="126"/>
-      <c r="I64" s="126"/>
+      <c r="H64" s="178"/>
+      <c r="I64" s="178"/>
       <c r="J64" s="60"/>
       <c r="K64" s="60"/>
     </row>
-    <row r="65" spans="1:11" ht="36">
+    <row r="65" spans="1:11" ht="36.6">
       <c r="A65" s="6"/>
       <c r="B65" s="86"/>
       <c r="C65" s="87"/>
@@ -3210,21 +3211,21 @@
       <c r="E65" s="88"/>
       <c r="F65" s="98"/>
       <c r="G65" s="73"/>
-      <c r="H65" s="127"/>
-      <c r="I65" s="127"/>
+      <c r="H65" s="179"/>
+      <c r="I65" s="179"/>
       <c r="J65" s="60"/>
       <c r="K65" s="59"/>
     </row>
-    <row r="66" spans="1:11" ht="15.75">
+    <row r="66" spans="1:11" ht="15.6">
       <c r="A66" s="6"/>
     </row>
-    <row r="67" spans="1:11" ht="15.75">
+    <row r="67" spans="1:11" ht="15.6">
       <c r="A67" s="6"/>
     </row>
-    <row r="68" spans="1:11" ht="15.75">
+    <row r="68" spans="1:11" ht="15.6">
       <c r="A68" s="6"/>
     </row>
-    <row r="69" spans="1:11" ht="15.75">
+    <row r="69" spans="1:11" ht="15.6">
       <c r="A69" s="6"/>
     </row>
     <row r="70" spans="1:11">
@@ -3238,6 +3239,64 @@
     </row>
   </sheetData>
   <mergeCells count="74">
+    <mergeCell ref="D62:E62"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="H61:I61"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="H46:I46"/>
+    <mergeCell ref="H56:I56"/>
+    <mergeCell ref="H57:I57"/>
+    <mergeCell ref="H42:I42"/>
+    <mergeCell ref="H47:I47"/>
+    <mergeCell ref="H48:I48"/>
+    <mergeCell ref="H54:I54"/>
+    <mergeCell ref="H55:I55"/>
+    <mergeCell ref="H43:I43"/>
+    <mergeCell ref="C57:G57"/>
+    <mergeCell ref="H58:I58"/>
+    <mergeCell ref="C61:G61"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="H63:I63"/>
+    <mergeCell ref="H64:I64"/>
+    <mergeCell ref="H65:I65"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="H62:I62"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="F14:G15"/>
+    <mergeCell ref="H14:I15"/>
+    <mergeCell ref="J15:J16"/>
+    <mergeCell ref="C17:I17"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="K15:K16"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="J7:K7"/>
     <mergeCell ref="C49:G49"/>
     <mergeCell ref="C2:E2"/>
     <mergeCell ref="F2:G2"/>
@@ -3254,64 +3313,6 @@
     <mergeCell ref="C6:E6"/>
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="J6:K6"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="K15:K16"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="F14:G15"/>
-    <mergeCell ref="H14:I15"/>
-    <mergeCell ref="J15:J16"/>
-    <mergeCell ref="C17:I17"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="H37:I37"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="H63:I63"/>
-    <mergeCell ref="H64:I64"/>
-    <mergeCell ref="H65:I65"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="H62:I62"/>
-    <mergeCell ref="D62:E62"/>
-    <mergeCell ref="H36:I36"/>
-    <mergeCell ref="H61:I61"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="H46:I46"/>
-    <mergeCell ref="H56:I56"/>
-    <mergeCell ref="H57:I57"/>
-    <mergeCell ref="H42:I42"/>
-    <mergeCell ref="H47:I47"/>
-    <mergeCell ref="H48:I48"/>
-    <mergeCell ref="H54:I54"/>
-    <mergeCell ref="H55:I55"/>
-    <mergeCell ref="H43:I43"/>
-    <mergeCell ref="C57:G57"/>
-    <mergeCell ref="H58:I58"/>
-    <mergeCell ref="C61:G61"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="25" fitToHeight="0" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
